--- a/database/Doctors_Dataset_MigraHealth_Kerala.xlsx
+++ b/database/Doctors_Dataset_MigraHealth_Kerala.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Doctor Directory" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Doctor Directory'!$A$3:$K$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Doctor Directory'!$A$3:$K$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -542,7 +542,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Government of Kerala — Health Service Department | 52 Approved Doctors | Auto-updated on every approval</t>
+          <t>Government of Kerala — Health Service Department | 51 Approved Doctors | Auto-updated on every approval</t>
         </is>
       </c>
     </row>
@@ -3366,17 +3366,17 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>General Physician</t>
+          <t>Dentist</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>MBBS</t>
+          <t>BDS</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Govt Hospital</t>
+          <t>Smile Clinic, Kollam</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
@@ -3386,16 +3386,16 @@
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>9123456789</t>
+          <t>9052435883</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>rajeshkumar@health.kerala.gov.in</t>
+          <t>rajeshkumar@gov.in</t>
         </is>
       </c>
       <c r="I54" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
@@ -3408,63 +3408,8 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>D052</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>Dr. Vijay Kumar</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>Pediatrician</t>
-        </is>
-      </c>
-      <c r="D55" s="10" t="inlineStr">
-        <is>
-          <t>MBBS</t>
-        </is>
-      </c>
-      <c r="E55" s="10" t="inlineStr">
-        <is>
-          <t>Govt Hospital</t>
-        </is>
-      </c>
-      <c r="F55" s="9" t="inlineStr">
-        <is>
-          <t>Palakkad</t>
-        </is>
-      </c>
-      <c r="G55" s="11" t="inlineStr">
-        <is>
-          <t>9898989812</t>
-        </is>
-      </c>
-      <c r="H55" s="9" t="inlineStr">
-        <is>
-          <t>vijaykumar@health.kerala.gov.in</t>
-        </is>
-      </c>
-      <c r="I55" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="J55" s="9" t="inlineStr">
-        <is>
-          <t>vijay.kumar</t>
-        </is>
-      </c>
-      <c r="K55" s="9" t="inlineStr">
-        <is>
-          <t>Self-Registered</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:K55"/>
+  <autoFilter ref="A3:K54"/>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
